--- a/backtest_runs/20260410_193731/by_symbol/GVGL/GVGL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GVGL/GVGL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-1418.580000000002</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>106833.16</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>106833.16</v>
@@ -679,7 +679,7 @@
         <v>-4615.380000000005</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>102217.78</v>
@@ -771,7 +771,7 @@
         <v>-2057.940000000002</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100339.66</v>
@@ -909,7 +909,7 @@
         <v>-4115.880000000005</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>96223.77999999998</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>96223.77999999998</v>
@@ -1047,7 +1047,7 @@
         <v>-5714.279999999999</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>97542.45999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-9430.559999999998</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>88111.89999999998</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>88111.89999999998</v>
@@ -1553,7 +1553,7 @@
         <v>-8471.520000000004</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>79640.37999999998</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>86573.43999999997</v>
